--- a/artfynd/A 12372-2022 artfynd.xlsx
+++ b/artfynd/A 12372-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12372-2022 artfynd.xlsx
+++ b/artfynd/A 12372-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74387800</v>
+        <v>74387801</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376314.2339380856</v>
+        <v>376313</v>
       </c>
       <c r="R2" t="n">
-        <v>6700777.088603038</v>
+        <v>6700777</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,19 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74387795</v>
+        <v>74387792</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376412.9559217681</v>
+        <v>376413</v>
       </c>
       <c r="R3" t="n">
-        <v>6700914.071147212</v>
+        <v>6700914</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74387801</v>
+        <v>74387798</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376313.2450694351</v>
+        <v>376332</v>
       </c>
       <c r="R4" t="n">
-        <v>6700777.122342495</v>
+        <v>6700784</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,16 +969,11 @@
         <v>74387799</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376319.9421758638</v>
+        <v>376320</v>
       </c>
       <c r="R5" t="n">
-        <v>6700784.801014573</v>
+        <v>6700785</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74387798</v>
+        <v>74387800</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376331.7917350754</v>
+        <v>376314</v>
       </c>
       <c r="R6" t="n">
-        <v>6700783.902557665</v>
+        <v>6700777</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 12372-2022 artfynd.xlsx
+++ b/artfynd/A 12372-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387801</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387792</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387798</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387799</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,8 +1182,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387800</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>